--- a/tools/importer/reports/import-homepage.report.xlsx
+++ b/tools/importer/reports/import-homepage.report.xlsx
@@ -52,7 +52,7 @@
     <t>homepage</t>
   </si>
   <si>
-    <t>2026-05-12T14:21:11.797Z</t>
+    <t>2026-05-26T14:08:17.652Z</t>
   </si>
   <si>
     <t>Insurance and Financial Services Company – Nationwide</t>
